--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486812_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486812_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4895</v>
+        <v>-1.1115</v>
       </c>
       <c r="E2" t="n">
-        <v>2.405</v>
+        <v>0.8537</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9155</v>
+        <v>-1.9652</v>
       </c>
       <c r="G2" t="n">
         <v>-1.113</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>1.456</v>
+        <v>-0.145</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4335</v>
+        <v>-0.1178</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0224</v>
+        <v>-0.0272</v>
       </c>
       <c r="V2" t="n">
         <v>1.8842</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-1.1447</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0274</v>
+        <v>-1.3377</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2426</v>
+        <v>0.193</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9447</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.353</v>
+        <v>-0.0069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5239</v>
+        <v>0.2137</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1709</v>
+        <v>-0.2206</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.0722</v>
+        <v>-1.8695</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5935</v>
+        <v>-1.4901</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4788</v>
+        <v>-0.3794</v>
       </c>
       <c r="G4" t="n">
         <v>-1.5868</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4855</v>
+        <v>-0.2827</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2759</v>
+        <v>-0.1725</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2096</v>
+        <v>-0.1102</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>H. CARRON GRILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.7193</v>
+        <v>-2.8042</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9807</v>
+        <v>-1.2145</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7386</v>
+        <v>-1.5897</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3457</v>
+        <v>-1.3461</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1791</v>
+        <v>0.3516</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1665</v>
+        <v>-1.6977</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6896</v>
+        <v>-0.6694</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6489</v>
+        <v>1.3177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>-1.9871</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0352</v>
+        <v>-0.6767</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.828</v>
+        <v>-0.9661</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2072</v>
+        <v>0.2893</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>-0.1931</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4083</v>
+        <v>-0.9448</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.352</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3252</v>
+        <v>-0.5927</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6565</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. CARRON GRILLO</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.9739</v>
+        <v>-2.9455</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1111</v>
+        <v>-2.1324</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8628</v>
+        <v>-0.8131</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3461</v>
+        <v>-1.3457</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3516</v>
+        <v>-0.1791</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6977</v>
+        <v>-1.1665</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6694</v>
+        <v>0.6896</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3177</v>
+        <v>0.6489</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9871</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6767</v>
+        <v>-2.0352</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9661</v>
+        <v>-0.828</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2893</v>
+        <v>-1.2072</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1931</v>
+        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1145</v>
+        <v>-0.6344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2486</v>
+        <v>-0.2347</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8659</v>
+        <v>-0.3997</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8995</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4019</v>
+        <v>-2.9497</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2601</v>
+        <v>-0.5844</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1418</v>
+        <v>-2.3653</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9193</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9693</v>
+        <v>-1.5171</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5451</v>
+        <v>-0.8694</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4242</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.3282</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PIZARRO</t>
+          <t>J. ARENAS CUESTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6038</v>
+        <v>-3.3727</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9947</v>
+        <v>-3.076</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6091</v>
+        <v>-0.2967</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8159</v>
+        <v>-2.3246</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1724</v>
+        <v>-1.5447</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6435</v>
+        <v>-0.7799</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2221</v>
+        <v>-1.9864</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-1.3376</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5674</v>
+        <v>-0.6488</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5937</v>
+        <v>-0.3382</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5176</v>
+        <v>-0.2071</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0761</v>
+        <v>-0.1311</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7723</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6455</v>
+        <v>-0.0827</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7725</v>
+        <v>-0.1242</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1271</v>
+        <v>0.0415</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0852</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARENAS CUESTA</t>
+          <t>M. PIZARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6044</v>
+        <v>-3.5997</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2828</v>
+        <v>-1.8913</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3215</v>
+        <v>-1.7084</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3246</v>
+        <v>-3.8159</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5447</v>
+        <v>-2.1724</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7799</v>
+        <v>-1.6435</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9864</v>
+        <v>-1.2221</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3376</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>-0.5674</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3382</v>
+        <v>-2.5937</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2071</v>
+        <v>-1.5176</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1311</v>
+        <v>-1.0761</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3144</v>
+        <v>-0.6414</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3311</v>
+        <v>-0.6691</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0167</v>
+        <v>0.0278</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.0852</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7137</v>
+        <v>-3.7178</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7541</v>
+        <v>-2.8575</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9596</v>
+        <v>-0.8603</v>
       </c>
       <c r="G10" t="n">
         <v>-5.865</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3202</v>
+        <v>-0.3243</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3038</v>
+        <v>-0.4072</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0164</v>
+        <v>0.083</v>
       </c>
       <c r="V10" t="n">
         <v>1.3129</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ROLDAN GAYOSO</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6559</v>
+        <v>-4.5681</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9695</v>
+        <v>-2.1049</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6864</v>
+        <v>-2.4632</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0394</v>
+        <v>-2.7475</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.986</v>
+        <v>-3.2901</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0534</v>
+        <v>0.5425</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1753</v>
+        <v>0.7228</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2905</v>
+        <v>-1.1513</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1152</v>
+        <v>1.8741</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2147</v>
+        <v>-3.4703</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2765</v>
+        <v>-2.1387</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9382</v>
+        <v>-1.3316</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5446</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8962</v>
+        <v>-2.1239</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-1.4344</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2486</v>
+        <v>-0.7038</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1768</v>
+        <v>-0.7306</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>M. ROLDAN GAYOSO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4673</v>
+        <v>-4.8324</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7806</v>
+        <v>-3.1212</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6867</v>
+        <v>-1.7112</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7475</v>
+        <v>-3.0394</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2901</v>
+        <v>-1.986</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5425</v>
+        <v>-1.0534</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7228</v>
+        <v>0.1753</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1513</v>
+        <v>0.2905</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8741</v>
+        <v>-0.1152</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4703</v>
+        <v>-3.2147</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1387</v>
+        <v>-2.2765</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3316</v>
+        <v>-0.9382</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1239</v>
+        <v>-2.8962</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3336</v>
+        <v>-0.2483</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3796</v>
+        <v>-0.4003</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9540999999999999</v>
+        <v>0.1519</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8295</v>
+        <v>-5.1456</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8117</v>
+        <v>-2.9291</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0178</v>
+        <v>-2.2165</v>
       </c>
       <c r="G13" t="n">
         <v>-5.1924</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0079</v>
+        <v>-1.324</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6003</v>
+        <v>-0.7177</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4076</v>
+        <v>-0.6063</v>
       </c>
       <c r="V13" t="n">
         <v>0.9847</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-38.3372</v>
+        <v>-38.06140000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.1612</v>
+        <v>-21.8854</v>
       </c>
       <c r="F14" t="n">
         <v>-16.176</v>
@@ -1525,7 +1525,7 @@
         <v>-2.7516</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.2715</v>
+        <v>-2.271500000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-27.2173</v>
@@ -1546,19 +1546,19 @@
         <v>10.6192</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.8621</v>
+        <v>-7.586</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.831199999999999</v>
+        <v>-4.555</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.0309</v>
+        <v>-3.0308</v>
       </c>
       <c r="V14" t="n">
         <v>3.6957</v>
       </c>
       <c r="W14" t="n">
-        <v>0.243</v>
+        <v>0.2430000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>3.4528</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.0052</v>
+        <v>6.7641</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3926</v>
+        <v>3.1516</v>
       </c>
       <c r="F15" t="n">
         <v>3.6126</v>
@@ -1624,10 +1624,10 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6754</v>
+        <v>1.4344</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0681</v>
+        <v>0.827</v>
       </c>
       <c r="U15" t="n">
         <v>0.6074000000000001</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1258</v>
+        <v>5.8187</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4534</v>
+        <v>3.736</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6724</v>
+        <v>2.0828</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3989</v>
+        <v>4.6837</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7102</v>
+        <v>2.3303</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6887</v>
+        <v>2.3534</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4965</v>
+        <v>4.1128</v>
       </c>
       <c r="K16" t="n">
-        <v>2.642</v>
+        <v>2.1934</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8545</v>
+        <v>1.9194</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9024</v>
+        <v>0.5709</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0682</v>
+        <v>0.137</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8341</v>
+        <v>0.434</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9626</v>
+        <v>0.8414</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5441</v>
+        <v>0.303</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4185</v>
+        <v>0.5384</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6565</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.5292</v>
+        <v>4.8597</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3223</v>
+        <v>1.8329</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2069</v>
+        <v>3.0268</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6837</v>
+        <v>4.3989</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3303</v>
+        <v>2.7102</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3534</v>
+        <v>1.6887</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1128</v>
+        <v>3.4965</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1934</v>
+        <v>2.642</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9194</v>
+        <v>0.8545</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5709</v>
+        <v>0.9024</v>
       </c>
       <c r="N17" t="n">
-        <v>0.137</v>
+        <v>0.0682</v>
       </c>
       <c r="O17" t="n">
-        <v>0.434</v>
+        <v>0.8341</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.6965</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1107</v>
+        <v>0.9236</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6626</v>
+        <v>0.7728</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5217</v>
+        <v>4.6996</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0525</v>
+        <v>2.1559</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4692</v>
+        <v>2.5437</v>
       </c>
       <c r="G18" t="n">
         <v>2.5411</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>0.629</v>
+        <v>0.8069</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0273</v>
+        <v>0.1307</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6017</v>
+        <v>0.6762</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.0803</v>
+        <v>4.6486</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2714</v>
+        <v>1.9326</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8089</v>
+        <v>2.716</v>
       </c>
       <c r="G19" t="n">
-        <v>4.7873</v>
+        <v>5.4828</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0624</v>
+        <v>3.0617</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7249</v>
+        <v>2.4211</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7607</v>
+        <v>4.9738</v>
       </c>
       <c r="K19" t="n">
-        <v>2.925</v>
+        <v>2.8555</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8357</v>
+        <v>2.1183</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0266</v>
+        <v>0.509</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1374</v>
+        <v>0.2061</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1108</v>
+        <v>0.3029</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5134</v>
+        <v>0.1312</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4966</v>
+        <v>-0.1451</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>0.2763</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0273</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.0273</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.8335</v>
+        <v>4.0429</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4154</v>
+        <v>2.5817</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4181</v>
+        <v>1.4613</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4828</v>
+        <v>4.7873</v>
       </c>
       <c r="H20" t="n">
-        <v>3.0617</v>
+        <v>3.0624</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4211</v>
+        <v>1.7249</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9738</v>
+        <v>4.7607</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8555</v>
+        <v>2.925</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1183</v>
+        <v>1.8357</v>
       </c>
       <c r="M20" t="n">
-        <v>0.509</v>
+        <v>0.0266</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2061</v>
+        <v>0.1374</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3029</v>
+        <v>-0.1108</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.1931</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.8962</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6839</v>
+        <v>0.476</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6622</v>
+        <v>-0.1864</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0217</v>
+        <v>0.6624</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0273</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-1.0273</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.0727</v>
+        <v>3.6313</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1289</v>
+        <v>1.4392</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9438</v>
+        <v>2.1921</v>
       </c>
       <c r="G21" t="n">
         <v>2.4108</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2758</v>
+        <v>0.8344</v>
       </c>
       <c r="T21" t="n">
-        <v>0.11</v>
+        <v>0.4203</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1658</v>
+        <v>0.4141</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.7007</v>
+        <v>2.9779</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6405</v>
+        <v>1.7439</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0602</v>
+        <v>1.234</v>
       </c>
       <c r="G22" t="n">
         <v>1.8953</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4192</v>
+        <v>0.6965</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4411</v>
+        <v>0.5445</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0219</v>
+        <v>0.1519</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5642</v>
+        <v>0.6238</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9217</v>
+        <v>-0.9589</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4859</v>
+        <v>1.5827</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4166</v>
+        <v>1.352</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1861</v>
+        <v>-1.2275</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2305</v>
+        <v>2.5794</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0453</v>
+        <v>1.6148</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1581</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2035</v>
+        <v>2.5659</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3713</v>
+        <v>-0.2629</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3442</v>
+        <v>-0.2764</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0271</v>
+        <v>0.0135</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9654</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>0.866</v>
+        <v>0.3724</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7168</v>
+        <v>0.0135</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1492</v>
+        <v>0.3589</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.6838</v>
+        <v>-0.3282</v>
       </c>
       <c r="W23" t="n">
-        <v>-1.6838</v>
+        <v>-0.6565</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0961</v>
+        <v>0.2706</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5794</v>
+        <v>-1.4388</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4833</v>
+        <v>1.7094</v>
       </c>
       <c r="G24" t="n">
-        <v>1.352</v>
+        <v>0.4166</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2275</v>
+        <v>0.1861</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5794</v>
+        <v>0.2305</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6148</v>
+        <v>0.0453</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.1581</v>
       </c>
       <c r="L24" t="n">
-        <v>2.5659</v>
+        <v>0.2035</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2629</v>
+        <v>0.3713</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2764</v>
+        <v>0.3442</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0135</v>
+        <v>0.0271</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3475</v>
+        <v>0.5724</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.607</v>
+        <v>0.1997</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2595</v>
+        <v>0.3727</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3282</v>
+        <v>-1.6838</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6565</v>
+        <v>-1.6838</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2362,10 +2362,10 @@
         <v>38.3372</v>
       </c>
       <c r="E25" t="n">
-        <v>16.1759</v>
+        <v>16.1761</v>
       </c>
       <c r="F25" t="n">
-        <v>22.1613</v>
+        <v>22.1614</v>
       </c>
       <c r="G25" t="n">
         <v>32.2403</v>
@@ -2404,13 +2404,13 @@
         <v>12.55</v>
       </c>
       <c r="S25" t="n">
-        <v>7.861899999999999</v>
+        <v>7.862099999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>3.0309</v>
+        <v>3.0308</v>
       </c>
       <c r="U25" t="n">
-        <v>4.8311</v>
+        <v>4.831100000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-3.6958</v>
